--- a/feature_extraction_report.xlsx
+++ b/feature_extraction_report.xlsx
@@ -417,21 +417,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -489,6 +476,26 @@
           <t>prod_usage_pct</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>assigned</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>manual_covered</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>manual_review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>manual_blocked</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -501,50 +508,48 @@
           <t>Connector × Feature (payload-level, PM-agnostic)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="C2" t="n">
+        <v>181</v>
+      </c>
+      <c r="D2" t="n">
+        <v>88</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I2" t="n">
+        <v>125</v>
+      </c>
+      <c r="J2" t="n">
+        <v>36</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
+      </c>
+      <c r="L2" t="n">
+        <v>118</v>
+      </c>
+      <c r="M2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -558,50 +563,48 @@
           <t>Connector × PM × PMT × Feature</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="C3" t="n">
+        <v>676</v>
+      </c>
+      <c r="D3" t="n">
+        <v>315</v>
+      </c>
+      <c r="E3" t="n">
+        <v>258</v>
+      </c>
+      <c r="F3" t="n">
+        <v>103</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>43%</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>88</v>
+      </c>
+      <c r="I3" t="n">
+        <v>528</v>
+      </c>
+      <c r="J3" t="n">
+        <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -615,50 +618,48 @@
           <t>Core features (connector-agnostic)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C4" t="n">
+        <v>99</v>
+      </c>
+      <c r="D4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" t="n">
+        <v>71</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="H4" t="n">
+        <v>51</v>
+      </c>
+      <c r="I4" t="n">
+        <v>35</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
+      </c>
+      <c r="L4" t="n">
+        <v>78</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -672,50 +673,48 @@
           <t>All buckets combined</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
+      <c r="C5" t="n">
+        <v>956</v>
+      </c>
+      <c r="D5" t="n">
+        <v>431</v>
+      </c>
+      <c r="E5" t="n">
+        <v>380</v>
+      </c>
+      <c r="F5" t="n">
+        <v>145</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>159</v>
+      </c>
+      <c r="I5" t="n">
+        <v>688</v>
+      </c>
+      <c r="J5" t="n">
+        <v>109</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
+      </c>
+      <c r="L5" t="n">
+        <v>196</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/feature_extraction_report.xlsx
+++ b/feature_extraction_report.xlsx
@@ -512,17 +512,17 @@
         <v>181</v>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
         <v>42</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D3" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E3" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         <v>88</v>
       </c>
       <c r="I3" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -622,17 +622,17 @@
         <v>99</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -674,27 +674,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D5" t="n">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E5" t="n">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="F5" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>159</v>
       </c>
       <c r="I5" t="n">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="J5" t="n">
         <v>109</v>
